--- a/plate3d/PLATE3D_SAMPLE.xlsx
+++ b/plate3d/PLATE3D_SAMPLE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="94">
   <si>
     <t>PLATE3D example</t>
   </si>
@@ -220,10 +220,16 @@
     <t>XY</t>
   </si>
   <si>
+    <t>pl.rib_1</t>
+  </si>
+  <si>
     <t>YZ</t>
   </si>
   <si>
     <t>one module = one welded unit</t>
+  </si>
+  <si>
+    <t>pl.rib_2</t>
   </si>
   <si>
     <t>BASE</t>
@@ -1202,7 +1208,7 @@
         <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="E23" t="s">
         <v>16</v>
@@ -1217,12 +1223,12 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>64</v>
@@ -1231,7 +1237,7 @@
         <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
         <v>16</v>
@@ -1246,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1260,7 +1266,7 @@
         <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E25" t="s">
         <v>18</v>
@@ -1274,31 +1280,31 @@
         <v>17</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I27" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J27" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K27" t="s">
         <v>35</v>
@@ -1309,16 +1315,16 @@
         <v>17</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
         <v>65</v>
       </c>
       <c r="E28" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1335,16 +1341,16 @@
         <v>17</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s">
         <v>54</v>
       </c>
       <c r="E29" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1361,16 +1367,16 @@
         <v>17</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
         <v>42</v>
       </c>
       <c r="E30" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1387,16 +1393,16 @@
         <v>17</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
         <v>65</v>
       </c>
       <c r="E32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F32">
         <v>900</v>
@@ -1408,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -1416,16 +1422,16 @@
         <v>17</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D33" t="s">
         <v>65</v>
       </c>
       <c r="E33" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1445,16 +1451,16 @@
         <v>17</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D34" t="s">
         <v>65</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F34">
         <v>-3000</v>
@@ -1466,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J34">
         <v>45</v>
@@ -1480,16 +1486,16 @@
         <v>17</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1506,11 +1512,11 @@
         <v>17</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/plate3d/PLATE3D_SAMPLE.xlsx
+++ b/plate3d/PLATE3D_SAMPLE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="102">
   <si>
     <t>PLATE3D example</t>
   </si>
@@ -290,6 +290,30 @@
   </si>
   <si>
     <t>as.stack</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>ISO</t>
+  </si>
+  <si>
+    <t>SAMPLE - ISOMETRIC</t>
+  </si>
+  <si>
+    <t>PLOT</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>PLATES</t>
+  </si>
+  <si>
+    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -686,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -823,6 +847,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
@@ -886,6 +911,7 @@
         <v>24</v>
       </c>
     </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>17</v>
@@ -973,6 +999,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
@@ -1013,6 +1040,7 @@
         <v>1400</v>
       </c>
     </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>17</v>
@@ -1101,6 +1129,7 @@
         <v>13</v>
       </c>
     </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>17</v>
@@ -1275,6 +1304,7 @@
         <v>16</v>
       </c>
     </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>17</v>
@@ -1388,6 +1418,7 @@
         <v>620</v>
       </c>
     </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>17</v>
@@ -1481,6 +1512,7 @@
         <v>5</v>
       </c>
     </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>17</v>
@@ -1507,12 +1539,64 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B38" s="3" t="s">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>93</v>
+      </c>
+      <c r="C38" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" t="s">
+        <v>94</v>
+      </c>
+      <c r="G38">
+        <v>50</v>
+      </c>
+      <c r="H38" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" t="s">
+        <v>98</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" t="s">
+        <v>98</v>
+      </c>
+      <c r="E40">
+        <v>20</v>
+      </c>
+      <c r="F40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_SAMPLE.xlsx
+++ b/plate3d/PLATE3D_SAMPLE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="94">
   <si>
     <t>PLATE3D example</t>
   </si>
@@ -290,30 +290,6 @@
   </si>
   <si>
     <t>as.stack</t>
-  </si>
-  <si>
-    <t>VIEW</t>
-  </si>
-  <si>
-    <t>ISO</t>
-  </si>
-  <si>
-    <t>SAMPLE - ISOMETRIC</t>
-  </si>
-  <si>
-    <t>PLOT</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>PLATES</t>
-  </si>
-  <si>
-    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -710,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -847,7 +823,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
@@ -911,7 +886,6 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>17</v>
@@ -999,7 +973,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
@@ -1040,7 +1013,6 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>17</v>
@@ -1129,7 +1101,6 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>17</v>
@@ -1304,7 +1275,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>17</v>
@@ -1418,7 +1388,6 @@
         <v>620</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>17</v>
@@ -1512,7 +1481,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>17</v>
@@ -1539,64 +1507,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="C38" t="s">
-        <v>83</v>
-      </c>
-      <c r="D38" t="s">
-        <v>94</v>
-      </c>
-      <c r="G38">
-        <v>50</v>
-      </c>
-      <c r="H38" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>96</v>
-      </c>
-      <c r="C39" t="s">
-        <v>97</v>
-      </c>
-      <c r="D39" t="s">
-        <v>98</v>
-      </c>
-      <c r="E39">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>96</v>
-      </c>
-      <c r="C40" t="s">
-        <v>53</v>
-      </c>
-      <c r="D40" t="s">
-        <v>98</v>
-      </c>
-      <c r="E40">
-        <v>20</v>
-      </c>
-      <c r="F40" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
   </sheetData>
